--- a/worklog/v2.2.3/s10/v4/pjm/test/ods_tech_state_measure_v2.xlsx
+++ b/worklog/v2.2.3/s10/v4/pjm/test/ods_tech_state_measure_v2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="技术状态跟进措施表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ods_tech_state_measure_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,297 +413,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO9"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="16" customWidth="1" min="35" max="35"/>
-    <col width="21" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>技术状态项名称、代号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>更改事项</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>责任科室</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>分管室领导</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>更改提出时间</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>更改提出周数</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>技术状态变更单是否完成签署</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>技术状态变更单闭环签署时间</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>技术状态变更单闭环签署周数</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>简要更改原因及内容</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>更改类别</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>计划完成文件闭环签署时间</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>计划完成文件闭环签署周数</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>计划完成整改落实时间</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>计划完成整改落实周数</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>计划是否已在进度信息汇总表中更新</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>新增计划数量</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>受影响文件</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>受影响实物(PBS名称)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>文件签署状态</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>整改落实状态</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>项目主管</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>跟进措施类别</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>跟进措施题目</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>跟进人</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>主送</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>抄送</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>跟进时间</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>跟进周数</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>闭环状态</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>最终闭环时间</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>最终闭环周数</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>闭环交付物类别</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>闭环交付物</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>主要风险内容</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新时间</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新周数</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>填写人</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tech_state_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>change_item</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dept</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dept_leader</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>change_submit_time</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change_submit_week</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>completion_signature</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>signature_closure_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>signature_closure_week</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>change_category</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>plan_file_closure_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>plan_file_closure_week</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>plan_reform_date</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>plan_reform_week</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>plan_synced</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>new_plan_count</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>affected_files</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>affected_objects</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>file_signature_status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>reform_status</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>project_manager</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>measure_category</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>measure_title</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>follow_up_person</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>main_recipient</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>cc_recipient</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>follow_up_date</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>follow_up_week</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>closure_status</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>final_closure_date</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>final_closure_week</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>closure_deliverable_type</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>closure_deliverable</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>risk_content</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>last_update_time</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>last_update_week</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>filled_by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>控制器硬件</t>
+          <t>综合控制机</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>更换主控芯片型号</t>
+          <t>综合统筹平台技术状态调整</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>陈工</t>
+          <t>王工</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>总体室</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>赵总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>12</v>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -724,54 +671,62 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>原芯片供货延长</t>
+          <t>综合统筹平台关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>16</v>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>19</v>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>2</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HW-SPEC-A01-001;HW-BOM-A01-001</t>
+          <t>XM-2026-C01-SPEC-001;XM-2026-C01-DRAW-002</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>控制器主板</t>
+          <t>综合控制机机箱</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -791,22 +746,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>重要跟进</t>
+          <t>常规跟进</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>芯片更换签署跟进</t>
+          <t>综合统筹平台技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>陈工</t>
+          <t>王工</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>赵总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -816,11 +771,13 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>14</v>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -829,11 +786,13 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>19</v>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -842,162 +801,166 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>变更单;整改报告</t>
+          <t>技术状态闭环单;签署记录</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>芯片供货风险</t>
+          <t>综合统筹平台关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>19</v>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>已纳入技术状态跟踪</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>陈工</t>
+          <t>王工</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>发动机喷管</t>
+          <t>飞控控制器</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>喷管材料升级</t>
+          <t>飞控执行机构技术状态调整</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>15</v>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>飞控执行机构关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>性能要求提升</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>19</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ENG-SPEC-A02-001;ENG-MAT-A02-002</t>
+          <t>XM-2026-C02-SPEC-001;XM-2026-C02-DRAW-002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>喷管组件</t>
+          <t>飞控控制器样机</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>已评估评审，已签署</t>
+          <t>已提出需求，未评估评审</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>已落实整改</t>
+          <t>整改中</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>陈PM</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>重要跟进</t>
+          <t>专项跟进</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>材料升级变更单跟进</t>
+          <t>飞控执行机构技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1007,97 +970,89 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>已闭环</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>变更单;材料验证报告</t>
-        </is>
-      </c>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>材料适配风险</t>
+          <t>飞控执行机构关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>22</v>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>待完成文件签署</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>制导算法</t>
+          <t>动力控制组件</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>制导算法参数优化</t>
+          <t>姿轨动力系统技术状态调整</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>制导室</t>
+          <t>动力室</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>26</v>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1106,15 +1061,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>28</v>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>仿真偏差修正</t>
+          <t>姿轨动力系统关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1124,36 +1081,42 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>30</v>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>31</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>GUID-ALGO-B01-001</t>
+          <t>XM-2026-C03-SPEC-001;XM-2026-C03-DRAW-002</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>制导软件算法模块</t>
+          <t>动力控制组件</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1163,12 +1126,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>已落实整改</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>林PM</t>
+          <t>赵PM</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1178,17 +1141,17 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>算法参数变更跟进</t>
+          <t>姿轨动力系统技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1198,25 +1161,21 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>26</v>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
           <t>已闭环</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>31</v>
-      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>文件</t>
@@ -1224,80 +1183,86 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>变更单;仿真修正报告</t>
+          <t>技术状态闭环单;签署记录</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>仿真偏差</t>
+          <t>姿轨动力系统关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>31</v>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>已纳入技术状态跟踪</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>遥控协议</t>
+          <t>制导计算机</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>遥控软件协议版本升级</t>
+          <t>惯导制导系统技术状态调整</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>郭工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>制导室</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>朱总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>37</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>协议适配升级</t>
+          <t>惯导制导系统关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1307,41 +1272,47 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>43</v>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>47</v>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SW-PROTO-B02-001;SW-TEST-B02-002</t>
+          <t>XM-2026-C04-SPEC-001;XM-2026-C04-DRAW-002</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>遥控软件协议栈</t>
+          <t>制导计算机板卡</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>已提出需求，未评估评审</t>
+          <t>已评估评审，未签署</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1351,27 +1322,27 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>徐PM</t>
+          <t>林PM</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>重要跟进</t>
+          <t>专项跟进</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>协议升级评估跟进</t>
+          <t>惯导制导系统技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>郭工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>朱总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1381,84 +1352,89 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>38</v>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>评估计划</t>
-        </is>
-      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>协议兼容性</t>
+          <t>惯导制导系统关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>39</v>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>持续跟进</t>
+          <t>待完成文件签署</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>郭工</t>
+          <t>林工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>蓄电池组</t>
+          <t>实时软件构件</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>蓄电池管理策略优化</t>
+          <t>实时软件平台技术状态调整</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>28</v>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1467,15 +1443,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>30</v>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>循环性能优化</t>
+          <t>实时软件平台关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1485,36 +1463,42 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>32</v>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>34</v>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>1</v>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>BAT-MGMT-B03-001</t>
+          <t>XM-2026-C05-SPEC-001;XM-2026-C05-DRAW-002</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>电池管理软件</t>
+          <t>实时软件构件包</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1529,7 +1513,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>宋PM</t>
+          <t>沈PM</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1539,17 +1523,17 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>管理策略变更跟进</t>
+          <t>实时软件平台技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1559,11 +1543,13 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>29</v>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1572,11 +1558,13 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
@@ -1585,52 +1573,54 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>变更单;策略验证报告</t>
+          <t>技术状态闭环单;签署记录</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>循环性能</t>
+          <t>实时软件平台关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>34</v>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>已纳入技术状态跟踪</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>主承力结构</t>
+          <t>主承力舱段</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>主承力结构加强筋调整</t>
+          <t>复合结构组件技术状态调整</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1645,82 +1635,84 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>23</v>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>25</v>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>应力集中改进</t>
+          <t>复合结构组件关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>27</v>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>29</v>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>STR-SPEC-B04-001</t>
+          <t>XM-2026-C06-SPEC-001;XM-2026-C06-DRAW-002</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>主承力结构件</t>
+          <t>主承力舱段结构件</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>已评估评审，已签署</t>
+          <t>已提出需求，未签署</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>已落实整改</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>邓PM</t>
+          <t>周PM</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1730,12 +1722,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>加强筋变更跟进</t>
+          <t>复合结构组件技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1750,25 +1742,21 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>23</v>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
           <t>已闭环</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>29</v>
-      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>文件</t>
@@ -1776,162 +1764,166 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>变更单;仿真报告</t>
+          <t>技术状态闭环单;签署记录</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>应力集中</t>
+          <t>复合结构组件关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>29</v>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>待完成文件签署</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>测控主机</t>
+          <t>电源管理单元</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>测控主机备选元器件替换</t>
+          <t>高可靠电源系统技术状态调整</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>测控室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>21</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>高可靠电源系统关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>23</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>元器件到货归零</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>28</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>TC-HW-B05-001;TC-BOM-B05-002</t>
+          <t>XM-2026-C07-SPEC-001;XM-2026-C07-DRAW-002</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>测控主机单元</t>
+          <t>电源管理单元</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>已评估评审，已签署</t>
+          <t>已提出需求，未评估评审</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>已落实整改</t>
+          <t>整改中</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>田PM</t>
+          <t>宋PM</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>重要跟进</t>
+          <t>专项跟进</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>元器件替换变更跟进</t>
+          <t>高可靠电源系统技术状态调整跟进</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1941,232 +1933,633 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>21</v>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>已闭环</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>变更单;替换试验报告</t>
-        </is>
-      </c>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>元器件一致性</t>
+          <t>高可靠电源系统关键约束调整，需要更新技术状态与文件</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>28</v>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>待完成文件签署</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EMC设计</t>
+          <t>载荷处理模块</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EMC屏蔽与滤波设计优化</t>
+          <t>电子载荷组件技术状态调整</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>电子室</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>郑总</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>电子载荷组件关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>XM-2026-C08-SPEC-001;XM-2026-C08-DRAW-002</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>载荷处理模块</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>已评估评审，已签署</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>已落实整改</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>徐PM</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>常规跟进</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>电子载荷组件技术状态调整跟进</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>郑总</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>已闭环</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>技术状态闭环单;签署记录</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>电子载荷组件关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>已纳入技术状态跟踪</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>测控主机</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>测控链路系统技术状态调整</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>测控室</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>测控链路系统关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>XM-2026-C09-SPEC-001;XM-2026-C09-DRAW-002</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>测控主机样机</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>已提出需求，已签署</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>田PM</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>常规跟进</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>测控链路系统技术状态调整跟进</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>已闭环</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>技术状态闭环单;签署记录</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>测控链路系统关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>已纳入技术状态跟踪</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>综合试验工装</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台技术状态调整</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>柳工</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>试验室</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>曹总</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>38</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2027-01-11</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>40</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>EMC超标归零</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>43</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>48</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>EMC-DESIGN-B06-001;EMC-FILT-B06-002</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>综合试验件</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>已评估评审，已签署</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>XM-2026-C10-SPEC-001;XM-2026-C10-DRAW-002</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>综合试验工装</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>已评估评审，未签署</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>整改中</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>柳PM</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>重大跟进</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>EMC设计变更跟进</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>专项跟进</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台技术状态调整跟进</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>柳工</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>曹总</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>李所</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>EMC优化方案</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>EMC超标</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>45</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>持续跟进</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台关键约束调整，需要更新技术状态与文件</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>待完成文件签署</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>柳工</t>
         </is>
